--- a/file/Microsoft_Azure_Attestation_VPATJ08340.xlsx
+++ b/file/Microsoft_Azure_Attestation_VPATJ08340.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F05F8C91-D4DC-4892-BC2B-F5748A29D5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36CF12D2-05CE-4CDE-B1B3-23F97D0C955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{93D99186-85E8-428D-A2F6-E2A22A175D6B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{5D345F6B-D57A-4242-B839-338ECD776D04}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -37,35 +37,13 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
   <si>
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年9月22日</t>
+    <t>作成日：2025年10月23日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1635,70 +1613,59 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-    <v>Microsoft Azureのロゴ画像</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="Text" t="s"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>78664</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2120900</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>10237</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1" descr="Microsoft Azureのロゴ画像">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31AE3F9C-EA37-4CFA-B7EA-173128738067}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6083300" y="840664"/>
+          <a:ext cx="3498850" cy="1982623"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2017,8 +1984,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E5B4510-0335-4D4E-AEE0-E72446AE1914}">
-  <sheetPr codeName="Sheet282">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBB803-4303-4CF4-AFDE-186267F5C7FA}">
+  <sheetPr codeName="Sheet274">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2084,9 +2051,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="10" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
     </row>
@@ -2833,15 +2798,16 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{601D4501-BA4C-4F0B-8223-270CC68BB585}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{1052D3C8-9BB4-4454-B37A-33274A39848D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5BC63C-F2BC-4881-832D-6581EBE4A345}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF2BF2A7-80C1-4C0E-9B77-C489AD19BBF3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Microsoft_Azure_Attestation_VPATJ08340.xlsx
+++ b/file/Microsoft_Azure_Attestation_VPATJ08340.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36CF12D2-05CE-4CDE-B1B3-23F97D0C955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{314643E6-76A8-419A-9418-5D85AB9B46F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{5D345F6B-D57A-4242-B839-338ECD776D04}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{9C10C579-192B-4171-A6FC-A327086734A5}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2025年10月23日</t>
+    <t>作成日：2026年9月22日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1633,7 +1633,7 @@
         <xdr:cNvPr id="2" name="図 1" descr="Microsoft Azureのロゴ画像">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31AE3F9C-EA37-4CFA-B7EA-173128738067}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A94579EE-30AA-4F69-BD9D-137A14C4C39C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1984,8 +1984,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBB803-4303-4CF4-AFDE-186267F5C7FA}">
-  <sheetPr codeName="Sheet274">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE76D932-EAC9-4043-B810-259E92F09127}">
+  <sheetPr codeName="Sheet290">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2798,7 +2798,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{1052D3C8-9BB4-4454-B37A-33274A39848D}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{70F765BB-DAF6-4A5D-AC6F-8DEC53FBB55B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2807,7 +2807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF2BF2A7-80C1-4C0E-9B77-C489AD19BBF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FE8DEC-3D87-4793-89C1-448D2C7717F0}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
